--- a/02_DIA_inicio_2026_analisis_assets/rbd_9741_escuela-basica-republica-de-indonesia_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9741_escuela-basica-republica-de-indonesia_nt1_nucleos.xlsx
@@ -763,13 +763,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33BA800D-0C05-4E25-BEF9-8F936B18C7B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57CFE092-B358-4D6A-9168-1899C4967426}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA49C7D6-D913-41F4-BB24-A6AE457D0F40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F9EEDE9-600E-41DF-BF4D-31AE25E87FF0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33B6E261-AA8F-4BB6-81A2-276D85BF6F15}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2495A01F-3319-4B4B-9553-6D589187FD76}"/>
 </file>